--- a/docs/evidencias/S10/anexo_E_analisis_brechas.xlsx
+++ b/docs/evidencias/S10/anexo_E_analisis_brechas.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DICOSUR · PETI v0.10 · Restringido · Taller 10 SI-886</t>
+          <t>Municipalidad Distrital de Alto Selva · PETI v0.10 · Restringido · Taller 10 SI-886</t>
         </is>
       </c>
     </row>
@@ -550,35 +550,35 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Negocio</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Plataforma del ERP sin soporte del fabricante</t>
+          <t>Sin Comité ni Líder de Gobierno Digital designados</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>NOD-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>NOD-01O</t>
+          <t>ACT-09; ROL-05</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Modificar</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>AP-03 · A2 (3.3 PE-05) · E-05</t>
+          <t>AP-01 · H-01 · R.M. 119-2018-PCM</t>
         </is>
       </c>
     </row>
@@ -600,35 +600,35 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Negocio</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Respaldo sin prueba de restauración</t>
+          <t>Sin Plan de Gobierno Digital ni PETI aprobados</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>TSV-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>TSV-03O</t>
+          <t>PRO-09</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Modificar</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>AP-03 · D6 (3.1.4) · E-12</t>
+          <t>AP-01 · H-01 · H-02 · D. Leg. 1412</t>
         </is>
       </c>
     </row>
@@ -650,22 +650,22 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Negocio</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Servidor único sin redundancia</t>
+          <t>Sin dueños de dato designados por cargo</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>NOD-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>NOD-05</t>
+          <t>ROL-04</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>COBIT DSS04 (4.2) · D6 · E-12</t>
+          <t>AP-02 · H-09</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Sin registro de actividades de tratamiento</t>
+          <t>Datos personales sin registro de actividades de tratamiento</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -724,11 +724,11 @@
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>AP-04 · A3 (3.3 PE-09) · E-11</t>
+          <t>AP-07 · H-10 · Ley 29733 · D. S. 016-2024-JUS</t>
         </is>
       </c>
     </row>
@@ -750,45 +750,45 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Negocio</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Sin dueños de dato designados</t>
+          <t>Respaldo a disco local sin restauración probada ni copia fuera de la sede</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>TSV-03</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>TSV-03O; NOD-06</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Modificar</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>ROL-04</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>B-04</t>
-        </is>
-      </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>WP-03</t>
+          <t>WP-04</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>AP-01 · D7 (2.4)</t>
+          <t>AP-03 · H-05 · COBIT DSS04</t>
         </is>
       </c>
     </row>
@@ -800,22 +800,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Datos</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Cliente en tres lugares sin fuente ni dueño</t>
+          <t>Servidor único sin autonomía de energía</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>DO-01; DO-02; DO-03</t>
+          <t>NOD-01</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>DO-01</t>
+          <t>NOD-01O</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -824,21 +824,21 @@
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>B-05; B-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>WP-03</t>
+          <t>WP-04</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>AP-01 · D7 · E-09</t>
+          <t>AP-03 · H-04 · H-05</t>
         </is>
       </c>
     </row>
@@ -850,22 +850,22 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Datos</t>
+          <t>Aplicación</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Precio sin fuente autoritativa</t>
+          <t>Rentas y catastro con soporte vencido desde 2023</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>DO-05</t>
+          <t>APP-03</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>DO-05O</t>
+          <t>APP-03O</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -874,21 +874,21 @@
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>B-05</t>
+          <t>B-05; B-06</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>WP-03</t>
+          <t>WP-05</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>AP-01 · AP-06</t>
+          <t>AP-03 · AP-04 · H-04 · incidente (Ficha §G)</t>
         </is>
       </c>
     </row>
@@ -905,40 +905,40 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Integración por archivo plano nocturno</t>
+          <t>Trámite documentario sin soporte · código ni documentación</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>AIF-01</t>
+          <t>APP-02</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>APP-14; AIF-03</t>
+          <t>APP-02O</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Reemplazar</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>B-05; B-06</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>WP-04</t>
+          <t>WP-05</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>AP-02 · D3 · D4</t>
+          <t>AP-04 · H-03</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Stock con dos versiones (ERP y WMS)</t>
+          <t>Expediente sin fuente digital (el físico manda · 1 340 sin estado)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>DO-07; DO-08</t>
+          <t>DO-04; DO-05</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>DO-07O</t>
+          <t>DO-04O</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -974,11 +974,11 @@
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>B-08</t>
+          <t>B-03; B-08</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>AP-01 · AP-02</t>
+          <t>AP-02 · AP-05 · H-09</t>
         </is>
       </c>
     </row>
@@ -1000,22 +1000,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Aplicación</t>
+          <t>Datos</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Portal B2B sin integración</t>
+          <t>Deuda del contribuyente distinta en rentas y fiscalización</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>APP-02</t>
+          <t>DO-01; DO-02</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>APP-02O</t>
+          <t>DO-01</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>B-08; B-06; B-16</t>
+          <t>B-03; B-07</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>WP-05</t>
+          <t>WP-03</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Visión (2.2) · AP-05 · E-01</t>
+          <t>AP-02 · H-09</t>
         </is>
       </c>
     </row>
@@ -1050,45 +1050,45 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Negocio</t>
+          <t>Aplicación</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Toma de pedido por teléfono y papel</t>
+          <t>Mesa de partes virtual por formulario y correo que se imprime</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>PRO-02</t>
+          <t>APP-05; AIF-01</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>PRO-02O</t>
+          <t>AIF-04</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Modificar</t>
+          <t>Reemplazar</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>B-10</t>
+          <t>B-08</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>WP-05</t>
+          <t>WP-06</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>AP-05 · D3 (3.1.1 CV-05) · E-08</t>
+          <t>AP-06 · H-06</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Ruteo en hoja de cálculo</t>
+          <t>Integraciones manuales (correo impreso · recaudación digitada al SIAF-SP)</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>APP-06</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>APP-13; ASV-04</t>
+          <t>APP-11; AIF-03</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1124,21 +1124,21 @@
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>B-08; B-09</t>
+          <t>B-07; B-08</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>WP-06</t>
+          <t>WP-07</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>AP-06 · D4 (3.1.1 CV-03) · E-02</t>
+          <t>AP-06 · H-06 · D. Leg. 1412</t>
         </is>
       </c>
     </row>
@@ -1150,22 +1150,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Aplicación</t>
+          <t>Negocio</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Análisis comercial en hojas de cálculo</t>
+          <t>Registro civil en papel · sin sistema</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>APP-11</t>
+          <t>PRO-04</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>APP-15</t>
+          <t>PRO-04O; APP-12; DO-10</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1174,21 +1174,21 @@
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>B-04; B-06; B-07</t>
+          <t>B-04; B-12</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>WP-07</t>
+          <t>WP-06</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>D1 (3.1.5) · E-07</t>
+          <t>AP-05 · AP-06 · H-08</t>
         </is>
       </c>
     </row>
@@ -1205,40 +1205,40 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Reclamo por correo sin registro ni seguimiento</t>
+          <t>Licencias con fuente en el archivo físico y plazos discrepantes</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>PRO-08</t>
+          <t>PRO-03; DO-06</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>PRO-08O; APP-16</t>
+          <t>PRO-03O; DO-06O</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Modificar</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>B-06</t>
+          <t>B-08</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>WP-08</t>
+          <t>WP-06</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>ITIL / COBIT DSS02 (4.2) · A1 · E-06</t>
+          <t>AP-05 · H-07</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Hojas de clientes · precios · cobranza y personal operan como sistema</t>
+          <t>Tres hojas de cálculo operan como sistema</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>APP-07; APP-08; APP-09; APP-10</t>
+          <t>APP-06; APP-07; APP-08</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1274,21 +1274,21 @@
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>B-06; B-07; B-13</t>
+          <t>B-09; B-10; B-14</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>WP-07</t>
+          <t>WP-03</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>AP-06</t>
+          <t>AP-05 · H-07</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Aplicación</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Portal dependiente de un solo desarrollador</t>
+          <t>Red plana sin segmentación y sin segundo factor</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>APP-02</t>
+          <t>NET-01</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>APP-02O</t>
+          <t>NET-01O; TSV-05</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1324,21 +1324,121 @@
         </is>
       </c>
       <c r="G20" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>B-06</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>WP-02</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>AP-07 · H-10 · H-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>B-17</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Gestión de TI informal: cambios sin registro · incidentes en cuaderno · sin inventario de activos</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>APP-13; DO-11</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>WP-09</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>AP-07 · D2 (3.1.3) · E-10</t>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>WP-08</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>AP-04 · H-12 · COBIT BAI06 y DSS02</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>B-18</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Atención al ciudadano sin seguimiento del trámite</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>PRO-06</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>PRO-06O; ASV-06</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Modificar</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>B-11</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>WP-06</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>AP-06 · H-06</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1375,7 +1475,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DICOSUR · PETI v0.10 · Restringido · Taller 10 SI-886</t>
+          <t>Municipalidad Distrital de Alto Selva · PETI v0.10 · Restringido · Taller 10 SI-886</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1529,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Continuidad y plataforma del ERP</t>
+          <t>Gobierno digital y de TI</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1444,11 +1544,11 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>P-01 · P-03</t>
+          <t>P-01 Comité · Líder y Plan de Gobierno Digital</t>
         </is>
       </c>
       <c r="G5" s="6">
-        <f>SUMIF(Brechas!$I$5:$I$20,B5,Brechas!$G$5:$G$20)</f>
+        <f>SUMIF(Brechas!$I$5:$I$22,B5,Brechas!$G$5:$G$22)</f>
         <v/>
       </c>
     </row>
@@ -1460,17 +1560,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>WP-02</t>
+          <t>WP-04</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Cumplimiento de datos personales</t>
+          <t>Continuidad de la infraestructura</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>B-05; B-06</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1480,47 +1580,47 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>P-02</t>
+          <t>P-04 Respaldo verificado y continuidad</t>
         </is>
       </c>
       <c r="G6" s="6">
-        <f>SUMIF(Brechas!$I$5:$I$20,B6,Brechas!$G$5:$G$20)</f>
+        <f>SUMIF(Brechas!$I$5:$I$22,B6,Brechas!$G$5:$G$22)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>WP-09</t>
+          <t>WP-02</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Gestión del conocimiento del portal</t>
+          <t>Protección de datos y seguridad</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>B-16</t>
+          <t>B-04; B-16</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WP-01; WP-04</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>P-09</t>
+          <t>P-02 Registro de tratamientos y seguridad de la información</t>
         </is>
       </c>
       <c r="G7" s="6">
-        <f>SUMIF(Brechas!$I$5:$I$20,B7,Brechas!$G$5:$G$20)</f>
+        <f>SUMIF(Brechas!$I$5:$I$22,B7,Brechas!$G$5:$G$22)</f>
         <v/>
       </c>
     </row>
@@ -1532,103 +1632,103 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
+          <t>WP-05</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Recuperación de sistemas críticos</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>B-07; B-08</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
           <t>WP-04</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Capa de integración por servicios</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>B-08</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>WP-01</t>
-        </is>
-      </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>P-12 (nuevo · propuesto para 7.1)</t>
+          <t>P-05 Rentas con soporte y gestión documental</t>
         </is>
       </c>
       <c r="G8" s="6">
-        <f>SUMIF(Brechas!$I$5:$I$20,B8,Brechas!$G$5:$G$20)</f>
+        <f>SUMIF(Brechas!$I$5:$I$22,B8,Brechas!$G$5:$G$22)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>WP-03</t>
+          <t>WP-08</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Gobierno del dato y maestros</t>
+          <t>Gestión de servicios de TI</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>B-05; B-06; B-07; B-09</t>
+          <t>B-17</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>WP-02; WP-04</t>
+          <t>WP-01</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>P-08 · P-06 (gobierno)</t>
+          <t>P-08 Mesa de ayuda · cambios e inventario de activos</t>
         </is>
       </c>
       <c r="G9" s="6">
-        <f>SUMIF(Brechas!$I$5:$I$20,B9,Brechas!$G$5:$G$20)</f>
+        <f>SUMIF(Brechas!$I$5:$I$22,B9,Brechas!$G$5:$G$22)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
+          <t>WP-07</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Interoperabilidad con el Estado</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>B-12</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
           <t>WP-05</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Canal digital integrado</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>B-10; B-11</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>WP-03; WP-04; WP-09</t>
-        </is>
-      </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>P-04 · P-07</t>
+          <t>P-07 Capa de interoperabilidad y conexión a la PIDE</t>
         </is>
       </c>
       <c r="G10" s="6">
-        <f>SUMIF(Brechas!$I$5:$I$20,B10,Brechas!$G$5:$G$20)</f>
+        <f>SUMIF(Brechas!$I$5:$I$22,B10,Brechas!$G$5:$G$22)</f>
         <v/>
       </c>
     </row>
@@ -1645,98 +1745,62 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Ruteo y trazabilidad de despacho</t>
+          <t>Servicios digitales al ciudadano</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>B-12</t>
+          <t>B-11; B-13; B-14; B-18</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>WP-03; WP-04</t>
+          <t>WP-02; WP-05; WP-07</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>P-05</t>
+          <t>P-06 Mesa de partes · licencias y registro civil digitales</t>
         </is>
       </c>
       <c r="G11" s="6">
-        <f>SUMIF(Brechas!$I$5:$I$20,B11,Brechas!$G$5:$G$20)</f>
+        <f>SUMIF(Brechas!$I$5:$I$22,B11,Brechas!$G$5:$G$22)</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>WP-07</t>
+          <t>WP-03</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Analítica y retiro de hojas de cálculo</t>
+          <t>Fuentes autoritativas y retiro de hojas</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>B-13; B-15</t>
+          <t>B-09; B-10; B-15</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>WP-02; WP-03</t>
+          <t>WP-01; WP-05; WP-06</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>P-06</t>
+          <t>P-03 Gobierno del dato municipal</t>
         </is>
       </c>
       <c r="G12" s="6">
-        <f>SUMIF(Brechas!$I$5:$I$20,B12,Brechas!$G$5:$G$20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>WP-08</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Atención de reclamos con trazabilidad</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>B-14</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>WP-03</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>P-11</t>
-        </is>
-      </c>
-      <c r="G13" s="6">
-        <f>SUMIF(Brechas!$I$5:$I$20,B13,Brechas!$G$5:$G$20)</f>
+        <f>SUMIF(Brechas!$I$5:$I$22,B12,Brechas!$G$5:$G$22)</f>
         <v/>
       </c>
     </row>
@@ -1751,11 +1815,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1783,15 +1847,20 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
+          <t>Reemplazar</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
           <t>Retirar</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Esfuerzo (sem-p)</t>
         </is>
@@ -1804,23 +1873,27 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIFS(Brechas!$B$5:$B$20,$A5,Brechas!$F$5:$F$20,"Nuevo")</f>
+        <f>COUNTIFS(Brechas!$B$5:$B$22,$A5,Brechas!$F$5:$F$22,"Nuevo")</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>COUNTIFS(Brechas!$B$5:$B$20,$A5,Brechas!$F$5:$F$20,"Modificar")</f>
+        <f>COUNTIFS(Brechas!$B$5:$B$22,$A5,Brechas!$F$5:$F$22,"Modificar")</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>COUNTIFS(Brechas!$B$5:$B$20,$A5,Brechas!$F$5:$F$20,"Retirar")</f>
+        <f>COUNTIFS(Brechas!$B$5:$B$22,$A5,Brechas!$F$5:$F$22,"Reemplazar")</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>SUM(B5:D5)</f>
+        <f>COUNTIFS(Brechas!$B$5:$B$22,$A5,Brechas!$F$5:$F$22,"Retirar")</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>SUMIF(Brechas!$B$5:$B$20,$A5,Brechas!$G$5:$G$20)</f>
+        <f>SUM(B5:E5)</f>
+        <v/>
+      </c>
+      <c r="G5" s="6">
+        <f>SUMIF(Brechas!$B$5:$B$22,$A5,Brechas!$G$5:$G$22)</f>
         <v/>
       </c>
     </row>
@@ -1831,23 +1904,27 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIFS(Brechas!$B$5:$B$20,$A6,Brechas!$F$5:$F$20,"Nuevo")</f>
+        <f>COUNTIFS(Brechas!$B$5:$B$22,$A6,Brechas!$F$5:$F$22,"Nuevo")</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>COUNTIFS(Brechas!$B$5:$B$20,$A6,Brechas!$F$5:$F$20,"Modificar")</f>
+        <f>COUNTIFS(Brechas!$B$5:$B$22,$A6,Brechas!$F$5:$F$22,"Modificar")</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>COUNTIFS(Brechas!$B$5:$B$20,$A6,Brechas!$F$5:$F$20,"Retirar")</f>
+        <f>COUNTIFS(Brechas!$B$5:$B$22,$A6,Brechas!$F$5:$F$22,"Reemplazar")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUM(B6:D6)</f>
+        <f>COUNTIFS(Brechas!$B$5:$B$22,$A6,Brechas!$F$5:$F$22,"Retirar")</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>SUMIF(Brechas!$B$5:$B$20,$A6,Brechas!$G$5:$G$20)</f>
+        <f>SUM(B6:E6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="6">
+        <f>SUMIF(Brechas!$B$5:$B$22,$A6,Brechas!$G$5:$G$22)</f>
         <v/>
       </c>
     </row>
@@ -1858,23 +1935,27 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIFS(Brechas!$B$5:$B$20,$A7,Brechas!$F$5:$F$20,"Nuevo")</f>
+        <f>COUNTIFS(Brechas!$B$5:$B$22,$A7,Brechas!$F$5:$F$22,"Nuevo")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS(Brechas!$B$5:$B$20,$A7,Brechas!$F$5:$F$20,"Modificar")</f>
+        <f>COUNTIFS(Brechas!$B$5:$B$22,$A7,Brechas!$F$5:$F$22,"Modificar")</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>COUNTIFS(Brechas!$B$5:$B$20,$A7,Brechas!$F$5:$F$20,"Retirar")</f>
+        <f>COUNTIFS(Brechas!$B$5:$B$22,$A7,Brechas!$F$5:$F$22,"Reemplazar")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>SUM(B7:D7)</f>
+        <f>COUNTIFS(Brechas!$B$5:$B$22,$A7,Brechas!$F$5:$F$22,"Retirar")</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>SUMIF(Brechas!$B$5:$B$20,$A7,Brechas!$G$5:$G$20)</f>
+        <f>SUM(B7:E7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="6">
+        <f>SUMIF(Brechas!$B$5:$B$22,$A7,Brechas!$G$5:$G$22)</f>
         <v/>
       </c>
     </row>
@@ -1885,23 +1966,27 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIFS(Brechas!$B$5:$B$20,$A8,Brechas!$F$5:$F$20,"Nuevo")</f>
+        <f>COUNTIFS(Brechas!$B$5:$B$22,$A8,Brechas!$F$5:$F$22,"Nuevo")</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>COUNTIFS(Brechas!$B$5:$B$20,$A8,Brechas!$F$5:$F$20,"Modificar")</f>
+        <f>COUNTIFS(Brechas!$B$5:$B$22,$A8,Brechas!$F$5:$F$22,"Modificar")</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>COUNTIFS(Brechas!$B$5:$B$20,$A8,Brechas!$F$5:$F$20,"Retirar")</f>
+        <f>COUNTIFS(Brechas!$B$5:$B$22,$A8,Brechas!$F$5:$F$22,"Reemplazar")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>SUM(B8:D8)</f>
+        <f>COUNTIFS(Brechas!$B$5:$B$22,$A8,Brechas!$F$5:$F$22,"Retirar")</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>SUMIF(Brechas!$B$5:$B$20,$A8,Brechas!$G$5:$G$20)</f>
+        <f>SUM(B8:E8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="6">
+        <f>SUMIF(Brechas!$B$5:$B$22,$A8,Brechas!$G$5:$G$22)</f>
         <v/>
       </c>
     </row>
@@ -1929,6 +2014,10 @@
       </c>
       <c r="F9" s="6">
         <f>SUM(F5:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="6">
+        <f>SUM(G5:G8)</f>
         <v/>
       </c>
     </row>
